--- a/_workspace/huni-launch-runway/08_system-screen/t51/reports/launch-screens-20260919.xlsx
+++ b/_workspace/huni-launch-runway/08_system-screen/t51/reports/launch-screens-20260919.xlsx
@@ -22,7 +22,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'구분요약'!$A$1:$D$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'일정'!$A$1:$J$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'외부의존'!$A$1:$C$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'미수록'!$A$1:$E$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'미수록'!$A$1:$F$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'결정안건'!$A$1:$C$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A30"/>
+  <dimension ref="A1:A33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="135" customWidth="1" min="1" max="1"/>
@@ -616,22 +616,43 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>미수록 시트: t48 이 넘긴 89건 중 받는 원장에 실재하는 것은 6건뿐이고, 83건은 어느 화면 원장에도 없습니다.</t>
+          <t>미수록 시트: t48 이 넘긴 89건 중 받는 원장에 같은 행 번호로 실재하는 것은 6건뿐이고, 83건은 그 번호를 찾을 수 없습니다.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>없는 것으로 확인된 것이지 못 찾은 것이 아닙니다. 다만 정말 불필요한 일인지 조사에서 빠진 일인지는 아직 판정하지 않았습니다.</t>
+          <t>「행 번호가 없다」와 「그 일이 없다」는 다릅니다 — 같은 기능이 다른 번호로 실려 있을 수 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr"/>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>실측: 쿠폰·공지는 webadmin 으로 넘겼지만 t48 의 shopby 원장에 쿠폰 18행·공지 11행이 다른 번호로 있습니다.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
+        <is>
+          <t>그래서 낱말 흔적으로 갈라 셌습니다 — 흔적 전무 6건(「빠진 일」의 하한) · 어딘가 흔적 있음 77건(넘긴 곳이 틀렸을 후보의 상한, 낱말 일치라 과다 계상).</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>어느 쪽도 확정이 아닙니다. 가리려면 webadmin·셀러어드민을 한 번 다시 훑어야 합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>DB 쓰기 0 · 라이브 접속 0 · 날짜 추정 0 · 숫자는 전부 assemble.py / schedule.py 가 계산했습니다.</t>
         </is>
@@ -55162,7 +55183,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E84"/>
+  <dimension ref="A1:F84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -55170,6 +55191,7 @@
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -55198,6 +55220,11 @@
           <t>원장상태</t>
         </is>
       </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>낱말흔적</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -55225,6 +55252,11 @@
           <t>부분</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>t50</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -55252,6 +55284,11 @@
           <t>미착수</t>
         </is>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>t48, t49, t50</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -55279,6 +55316,11 @@
           <t>미착수</t>
         </is>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>t48, t49, t50</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -55306,6 +55348,11 @@
           <t>미착수</t>
         </is>
       </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>t48, t49, t50</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -55333,6 +55380,11 @@
           <t>미착수</t>
         </is>
       </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>t48, t49, t50</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -55360,6 +55412,11 @@
           <t>미착수</t>
         </is>
       </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>t48, t49, t50</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -55387,6 +55444,11 @@
           <t>미실측</t>
         </is>
       </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>t48</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -55414,6 +55476,11 @@
           <t>부분</t>
         </is>
       </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>t48, t50</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -55441,6 +55508,11 @@
           <t>미착수</t>
         </is>
       </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>t49, t50</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -55468,6 +55540,11 @@
           <t>미착수</t>
         </is>
       </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>t48, t49, t50</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -55495,6 +55572,11 @@
           <t>미착수</t>
         </is>
       </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>t48</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -55522,6 +55604,11 @@
           <t>미착수</t>
         </is>
       </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>t48, t49</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -55549,6 +55636,11 @@
           <t>미착수</t>
         </is>
       </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -55576,6 +55668,11 @@
           <t>미착수</t>
         </is>
       </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>t50</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -55603,6 +55700,11 @@
           <t>미착수</t>
         </is>
       </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>t48, t50</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -55630,6 +55732,11 @@
           <t>미착수</t>
         </is>
       </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>t48, t49, t50</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -55657,6 +55764,11 @@
           <t>미착수</t>
         </is>
       </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>t48, t49, t50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -55684,6 +55796,11 @@
           <t>미착수</t>
         </is>
       </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>t48, t50</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -55711,6 +55828,11 @@
           <t>미착수</t>
         </is>
       </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>t48, t49, t50</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -55738,6 +55860,11 @@
           <t>미실측</t>
         </is>
       </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>t48</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -55765,6 +55892,11 @@
           <t>작동</t>
         </is>
       </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>t48, t49, t50</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -55792,6 +55924,11 @@
           <t>미착수</t>
         </is>
       </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>t48</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -55819,6 +55956,11 @@
           <t>작동</t>
         </is>
       </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -55846,6 +55988,11 @@
           <t>미착수</t>
         </is>
       </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>t48</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -55873,6 +56020,11 @@
           <t>작동</t>
         </is>
       </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>t48</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -55900,6 +56052,11 @@
           <t>작동</t>
         </is>
       </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>t48</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -55927,6 +56084,11 @@
           <t>작동</t>
         </is>
       </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>t48</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -55954,6 +56116,11 @@
           <t>작동</t>
         </is>
       </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>t48</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -55981,6 +56148,11 @@
           <t>작동</t>
         </is>
       </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>t48, t49</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -56008,6 +56180,11 @@
           <t>미착수</t>
         </is>
       </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>t48</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -56035,6 +56212,11 @@
           <t>미착수</t>
         </is>
       </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>t48, t49</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -56062,6 +56244,11 @@
           <t>미착수</t>
         </is>
       </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>t48, t50</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -56089,6 +56276,11 @@
           <t>미착수</t>
         </is>
       </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>t48, t49</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -56116,6 +56308,11 @@
           <t>작동</t>
         </is>
       </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>t48, t50</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -56143,6 +56340,11 @@
           <t>작동</t>
         </is>
       </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>t48, t50</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -56170,6 +56372,11 @@
           <t>작동</t>
         </is>
       </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>t48, t50</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -56197,6 +56404,11 @@
           <t>작동</t>
         </is>
       </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>t48, t49, t50</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -56224,6 +56436,11 @@
           <t>작동</t>
         </is>
       </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>t48, t49, t50</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -56251,6 +56468,11 @@
           <t>작동</t>
         </is>
       </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>t48, t49</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -56278,6 +56500,11 @@
           <t>미착수</t>
         </is>
       </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>t48</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -56305,6 +56532,11 @@
           <t>미착수</t>
         </is>
       </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>t48</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -56332,6 +56564,11 @@
           <t>미착수</t>
         </is>
       </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>t48, t49, t50</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -56359,6 +56596,11 @@
           <t>작동</t>
         </is>
       </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>t48, t49, t50</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -56386,6 +56628,11 @@
           <t>미착수</t>
         </is>
       </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>t48, t49, t50</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -56413,6 +56660,11 @@
           <t>미착수</t>
         </is>
       </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>t48</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -56440,6 +56692,11 @@
           <t>미착수</t>
         </is>
       </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>t48, t50</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -56467,6 +56724,11 @@
           <t>미착수</t>
         </is>
       </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>t48, t49, t50</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -56494,6 +56756,11 @@
           <t>미착수</t>
         </is>
       </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>t48</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -56521,6 +56788,11 @@
           <t>미착수</t>
         </is>
       </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>t48, t49, t50</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -56548,6 +56820,11 @@
           <t>부분</t>
         </is>
       </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>t48, t49, t50</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -56575,6 +56852,11 @@
           <t>부분</t>
         </is>
       </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>t48, t49, t50</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -56602,6 +56884,11 @@
           <t>작동</t>
         </is>
       </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>t48, t49, t50</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -56629,6 +56916,11 @@
           <t>구현-미검증</t>
         </is>
       </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>t48, t49, t50</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -56656,6 +56948,11 @@
           <t>부분</t>
         </is>
       </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>t48, t49, t50</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -56683,6 +56980,11 @@
           <t>부분</t>
         </is>
       </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>t48</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -56710,6 +57012,11 @@
           <t>미착수</t>
         </is>
       </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>t48, t49, t50</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -56737,6 +57044,11 @@
           <t>부분</t>
         </is>
       </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>t50</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -56764,6 +57076,11 @@
           <t>부분</t>
         </is>
       </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>t48, t49, t50</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -56791,6 +57108,11 @@
           <t>부분</t>
         </is>
       </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>t48, t49, t50</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -56818,6 +57140,11 @@
           <t>미착수</t>
         </is>
       </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>t48, t49, t50</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -56845,6 +57172,11 @@
           <t>미착수</t>
         </is>
       </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>t48, t49, t50</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -56872,6 +57204,11 @@
           <t>미착수</t>
         </is>
       </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>t48, t50</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -56899,6 +57236,11 @@
           <t>미착수</t>
         </is>
       </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>t48, t49, t50</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -56926,6 +57268,11 @@
           <t>미착수</t>
         </is>
       </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>t48, t49, t50</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -56953,6 +57300,11 @@
           <t>미착수</t>
         </is>
       </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -56980,6 +57332,11 @@
           <t>미착수</t>
         </is>
       </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>t48</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -57007,6 +57364,11 @@
           <t>미착수</t>
         </is>
       </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>t48, t50</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -57034,6 +57396,11 @@
           <t>미착수</t>
         </is>
       </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>t48, t49, t50</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -57061,6 +57428,11 @@
           <t>미착수</t>
         </is>
       </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -57088,6 +57460,11 @@
           <t>미착수</t>
         </is>
       </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -57115,6 +57492,11 @@
           <t>미착수</t>
         </is>
       </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>t48, t49, t50</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -57142,6 +57524,11 @@
           <t>미착수</t>
         </is>
       </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -57169,6 +57556,11 @@
           <t>미착수</t>
         </is>
       </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>t49, t50</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -57196,6 +57588,11 @@
           <t>미착수</t>
         </is>
       </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>t48, t50</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -57223,6 +57620,11 @@
           <t>미착수</t>
         </is>
       </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>t50</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -57250,6 +57652,11 @@
           <t>미착수</t>
         </is>
       </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>t48, t49</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -57277,6 +57684,11 @@
           <t>미착수</t>
         </is>
       </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>t48</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -57304,6 +57716,11 @@
           <t>미착수</t>
         </is>
       </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>t48, t49, t50</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -57331,6 +57748,11 @@
           <t>미착수</t>
         </is>
       </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>t48, t50</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -57358,6 +57780,11 @@
           <t>미착수</t>
         </is>
       </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>t48, t49, t50</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -57385,6 +57812,11 @@
           <t>미착수</t>
         </is>
       </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>t48, t49, t50</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -57412,6 +57844,11 @@
           <t>미착수</t>
         </is>
       </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>t48, t49, t50</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -57439,9 +57876,14 @@
           <t>미착수</t>
         </is>
       </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>t48, t49, t50</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E84"/>
+  <autoFilter ref="A1:F84"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
